--- a/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
@@ -542,10 +542,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -556,14 +556,14 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🩺 HealthMate AI — Selenium Web Frontend E2E Test Summary</t>
+          <t>🩺 HealthMate AI — Selenium Web Frontend E2E Test Summary (300 Test Cases)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 300+ Test Cases Verification Report | Generated: 2026-08-08 14:27:14</t>
+          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1255</v>
+        <v>1200</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1255</v>
+        <v>1200</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Personalized Diet Plans</t>
+          <t>Personalized Diet Recommendations</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Multi-Language (EN, HI, TE)</t>
+          <t>Multi-Language Support (EN, HI, TE)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Profile &amp; Security</t>
+          <t>Profile &amp; Security Verification</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Performance &amp; Latency</t>
+          <t>Performance &amp; Latency Benchmarks</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J302"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #1</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #1</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #2</t>
+          <t>Invalid Password Rejection - Test Case Iteration #2</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #3</t>
+          <t>Non-existent User Lookup - Test Case Iteration #3</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #4</t>
+          <t>Blank Field Input Validation - Test Case Iteration #4</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #5</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #5</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #6</t>
+          <t>New Patient Registration - Test Case Iteration #6</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #7</t>
+          <t>Duplicate Username Check - Test Case Iteration #7</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #8</t>
+          <t>Password Confirmation Match - Test Case Iteration #8</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #9</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #9</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #10</t>
+          <t>Latest Assessment Banner - Test Case Iteration #10</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #11</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #11</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #12</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #12</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #13</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #13</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #14</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #14</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #15</t>
+          <t>Diet Plan Generation - Test Case Iteration #15</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #16</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #16</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #17</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #17</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #18</t>
+          <t>Report Download Endpoint - Test Case Iteration #18</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #19</t>
+          <t>Phone Verification OTP - Test Case Iteration #19</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #20</t>
+          <t>Page Latency Check - Test Case Iteration #20</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #21</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #21</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #22</t>
+          <t>Invalid Password Rejection - Test Case Iteration #22</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #23</t>
+          <t>Non-existent User Lookup - Test Case Iteration #23</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #24</t>
+          <t>Blank Field Input Validation - Test Case Iteration #24</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #25</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #25</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #26</t>
+          <t>New Patient Registration - Test Case Iteration #26</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #27</t>
+          <t>Duplicate Username Check - Test Case Iteration #27</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #28</t>
+          <t>Password Confirmation Match - Test Case Iteration #28</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #29</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #29</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #30</t>
+          <t>Latest Assessment Banner - Test Case Iteration #30</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #31</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #31</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #32</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #32</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #33</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #33</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #34</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #34</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #35</t>
+          <t>Diet Plan Generation - Test Case Iteration #35</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #36</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #36</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #37</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #37</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #38</t>
+          <t>Report Download Endpoint - Test Case Iteration #38</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #39</t>
+          <t>Phone Verification OTP - Test Case Iteration #39</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #40</t>
+          <t>Page Latency Check - Test Case Iteration #40</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #41</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #41</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #42</t>
+          <t>Invalid Password Rejection - Test Case Iteration #42</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #43</t>
+          <t>Non-existent User Lookup - Test Case Iteration #43</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #44</t>
+          <t>Blank Field Input Validation - Test Case Iteration #44</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #45</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #45</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #46</t>
+          <t>New Patient Registration - Test Case Iteration #46</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #47</t>
+          <t>Duplicate Username Check - Test Case Iteration #47</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #48</t>
+          <t>Password Confirmation Match - Test Case Iteration #48</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #49</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #49</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #50</t>
+          <t>Latest Assessment Banner - Test Case Iteration #50</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #51</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #51</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #52</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #52</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #53</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #53</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #54</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #54</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #55</t>
+          <t>Diet Plan Generation - Test Case Iteration #55</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #56</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #56</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #57</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #57</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #58</t>
+          <t>Report Download Endpoint - Test Case Iteration #58</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #59</t>
+          <t>Phone Verification OTP - Test Case Iteration #59</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #60</t>
+          <t>Page Latency Check - Test Case Iteration #60</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #61</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #61</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #62</t>
+          <t>Invalid Password Rejection - Test Case Iteration #62</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #63</t>
+          <t>Non-existent User Lookup - Test Case Iteration #63</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #64</t>
+          <t>Blank Field Input Validation - Test Case Iteration #64</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #65</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #65</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #66</t>
+          <t>New Patient Registration - Test Case Iteration #66</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #67</t>
+          <t>Duplicate Username Check - Test Case Iteration #67</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #68</t>
+          <t>Password Confirmation Match - Test Case Iteration #68</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #69</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #69</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #70</t>
+          <t>Latest Assessment Banner - Test Case Iteration #70</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #71</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #71</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #72</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #72</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #73</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #73</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #74</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #74</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #75</t>
+          <t>Diet Plan Generation - Test Case Iteration #75</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #76</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #76</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #77</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #77</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #78</t>
+          <t>Report Download Endpoint - Test Case Iteration #78</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #79</t>
+          <t>Phone Verification OTP - Test Case Iteration #79</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #80</t>
+          <t>Page Latency Check - Test Case Iteration #80</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #81</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #81</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #82</t>
+          <t>Invalid Password Rejection - Test Case Iteration #82</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #83</t>
+          <t>Non-existent User Lookup - Test Case Iteration #83</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #84</t>
+          <t>Blank Field Input Validation - Test Case Iteration #84</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #85</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #85</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #86</t>
+          <t>New Patient Registration - Test Case Iteration #86</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #87</t>
+          <t>Duplicate Username Check - Test Case Iteration #87</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #88</t>
+          <t>Password Confirmation Match - Test Case Iteration #88</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #89</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #89</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #90</t>
+          <t>Latest Assessment Banner - Test Case Iteration #90</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #91</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #91</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #92</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #92</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #93</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #93</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #94</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #94</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #95</t>
+          <t>Diet Plan Generation - Test Case Iteration #95</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #96</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #96</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #97</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #97</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #98</t>
+          <t>Report Download Endpoint - Test Case Iteration #98</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #99</t>
+          <t>Phone Verification OTP - Test Case Iteration #99</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #100</t>
+          <t>Page Latency Check - Test Case Iteration #100</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #101</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #101</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #102</t>
+          <t>Invalid Password Rejection - Test Case Iteration #102</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #103</t>
+          <t>Non-existent User Lookup - Test Case Iteration #103</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #104</t>
+          <t>Blank Field Input Validation - Test Case Iteration #104</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #105</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #105</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #106</t>
+          <t>New Patient Registration - Test Case Iteration #106</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #107</t>
+          <t>Duplicate Username Check - Test Case Iteration #107</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #108</t>
+          <t>Password Confirmation Match - Test Case Iteration #108</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #109</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #109</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #110</t>
+          <t>Latest Assessment Banner - Test Case Iteration #110</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #111</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #111</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #112</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #112</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #113</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #113</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #114</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #114</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #115</t>
+          <t>Diet Plan Generation - Test Case Iteration #115</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #116</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #116</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #117</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #117</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #118</t>
+          <t>Report Download Endpoint - Test Case Iteration #118</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #119</t>
+          <t>Phone Verification OTP - Test Case Iteration #119</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #120</t>
+          <t>Page Latency Check - Test Case Iteration #120</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #121</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #121</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #122</t>
+          <t>Invalid Password Rejection - Test Case Iteration #122</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #123</t>
+          <t>Non-existent User Lookup - Test Case Iteration #123</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #124</t>
+          <t>Blank Field Input Validation - Test Case Iteration #124</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #125</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #125</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #126</t>
+          <t>New Patient Registration - Test Case Iteration #126</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #127</t>
+          <t>Duplicate Username Check - Test Case Iteration #127</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #128</t>
+          <t>Password Confirmation Match - Test Case Iteration #128</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #129</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #129</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #130</t>
+          <t>Latest Assessment Banner - Test Case Iteration #130</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #131</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #131</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #132</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #132</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #133</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #133</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #134</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #134</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #135</t>
+          <t>Diet Plan Generation - Test Case Iteration #135</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #136</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #136</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #137</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #137</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #138</t>
+          <t>Report Download Endpoint - Test Case Iteration #138</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #139</t>
+          <t>Phone Verification OTP - Test Case Iteration #139</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #140</t>
+          <t>Page Latency Check - Test Case Iteration #140</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #141</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #141</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #142</t>
+          <t>Invalid Password Rejection - Test Case Iteration #142</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #143</t>
+          <t>Non-existent User Lookup - Test Case Iteration #143</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #144</t>
+          <t>Blank Field Input Validation - Test Case Iteration #144</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #145</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #145</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #146</t>
+          <t>New Patient Registration - Test Case Iteration #146</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #147</t>
+          <t>Duplicate Username Check - Test Case Iteration #147</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #148</t>
+          <t>Password Confirmation Match - Test Case Iteration #148</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #149</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #149</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #150</t>
+          <t>Latest Assessment Banner - Test Case Iteration #150</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #151</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #151</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #152</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #152</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #153</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #153</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #154</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #154</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #155</t>
+          <t>Diet Plan Generation - Test Case Iteration #155</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #156</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #156</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #157</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #157</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #158</t>
+          <t>Report Download Endpoint - Test Case Iteration #158</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #159</t>
+          <t>Phone Verification OTP - Test Case Iteration #159</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #160</t>
+          <t>Page Latency Check - Test Case Iteration #160</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #161</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #161</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #162</t>
+          <t>Invalid Password Rejection - Test Case Iteration #162</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #163</t>
+          <t>Non-existent User Lookup - Test Case Iteration #163</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #164</t>
+          <t>Blank Field Input Validation - Test Case Iteration #164</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #165</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #165</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #166</t>
+          <t>New Patient Registration - Test Case Iteration #166</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #167</t>
+          <t>Duplicate Username Check - Test Case Iteration #167</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #168</t>
+          <t>Password Confirmation Match - Test Case Iteration #168</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #169</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #169</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #170</t>
+          <t>Latest Assessment Banner - Test Case Iteration #170</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #171</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #171</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #172</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #172</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #173</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #173</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #174</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #174</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #175</t>
+          <t>Diet Plan Generation - Test Case Iteration #175</t>
         </is>
       </c>
       <c r="E177" s="9" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #176</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #176</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #177</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #177</t>
         </is>
       </c>
       <c r="E179" s="9" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #178</t>
+          <t>Report Download Endpoint - Test Case Iteration #178</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #179</t>
+          <t>Phone Verification OTP - Test Case Iteration #179</t>
         </is>
       </c>
       <c r="E181" s="9" t="inlineStr">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #180</t>
+          <t>Page Latency Check - Test Case Iteration #180</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #181</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #181</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="I183" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #182</t>
+          <t>Invalid Password Rejection - Test Case Iteration #182</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #183</t>
+          <t>Non-existent User Lookup - Test Case Iteration #183</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="I185" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #184</t>
+          <t>Blank Field Input Validation - Test Case Iteration #184</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -10424,12 +10424,12 @@
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #185</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #185</t>
         </is>
       </c>
       <c r="E187" s="9" t="inlineStr">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #186</t>
+          <t>New Patient Registration - Test Case Iteration #186</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -10524,12 +10524,12 @@
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #187</t>
+          <t>Duplicate Username Check - Test Case Iteration #187</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #188</t>
+          <t>Password Confirmation Match - Test Case Iteration #188</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #189</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #189</t>
         </is>
       </c>
       <c r="E191" s="9" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="I191" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #190</t>
+          <t>Latest Assessment Banner - Test Case Iteration #190</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #191</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #191</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="I193" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #192</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #192</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #193</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #193</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #194</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #194</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #195</t>
+          <t>Diet Plan Generation - Test Case Iteration #195</t>
         </is>
       </c>
       <c r="E197" s="9" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="I197" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #196</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #196</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #197</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #197</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="I199" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #198</t>
+          <t>Report Download Endpoint - Test Case Iteration #198</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -11124,12 +11124,12 @@
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #199</t>
+          <t>Phone Verification OTP - Test Case Iteration #199</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="I201" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #200</t>
+          <t>Page Latency Check - Test Case Iteration #200</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #201</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #201</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #202</t>
+          <t>Invalid Password Rejection - Test Case Iteration #202</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #203</t>
+          <t>Non-existent User Lookup - Test Case Iteration #203</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
@@ -11374,12 +11374,12 @@
       </c>
       <c r="I205" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #204</t>
+          <t>Blank Field Input Validation - Test Case Iteration #204</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #205</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #205</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="I207" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #206</t>
+          <t>New Patient Registration - Test Case Iteration #206</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #207</t>
+          <t>Duplicate Username Check - Test Case Iteration #207</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="I209" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #208</t>
+          <t>Password Confirmation Match - Test Case Iteration #208</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #209</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #209</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="I211" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #210</t>
+          <t>Latest Assessment Banner - Test Case Iteration #210</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #211</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #211</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #212</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #212</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #213</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #213</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="I215" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #214</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #214</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #215</t>
+          <t>Diet Plan Generation - Test Case Iteration #215</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
@@ -11974,12 +11974,12 @@
       </c>
       <c r="I217" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #216</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #216</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -12024,12 +12024,12 @@
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #217</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #217</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #218</t>
+          <t>Report Download Endpoint - Test Case Iteration #218</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #219</t>
+          <t>Phone Verification OTP - Test Case Iteration #219</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="I221" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #220</t>
+          <t>Page Latency Check - Test Case Iteration #220</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -12224,12 +12224,12 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #221</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #221</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="I223" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #222</t>
+          <t>Invalid Password Rejection - Test Case Iteration #222</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #223</t>
+          <t>Non-existent User Lookup - Test Case Iteration #223</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="I225" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #224</t>
+          <t>Blank Field Input Validation - Test Case Iteration #224</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #225</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #225</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #226</t>
+          <t>New Patient Registration - Test Case Iteration #226</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #227</t>
+          <t>Duplicate Username Check - Test Case Iteration #227</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
@@ -12574,12 +12574,12 @@
       </c>
       <c r="I229" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #228</t>
+          <t>Password Confirmation Match - Test Case Iteration #228</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #229</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #229</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="I231" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #230</t>
+          <t>Latest Assessment Banner - Test Case Iteration #230</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #231</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #231</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="I233" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #232</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #232</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #233</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #233</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
@@ -12874,12 +12874,12 @@
       </c>
       <c r="I235" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #234</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #234</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #235</t>
+          <t>Diet Plan Generation - Test Case Iteration #235</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="I237" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #236</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #236</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -13024,12 +13024,12 @@
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #237</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #237</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
@@ -13074,12 +13074,12 @@
       </c>
       <c r="I239" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #238</t>
+          <t>Report Download Endpoint - Test Case Iteration #238</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #239</t>
+          <t>Phone Verification OTP - Test Case Iteration #239</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="I241" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #240</t>
+          <t>Page Latency Check - Test Case Iteration #240</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #241</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #241</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
@@ -13274,12 +13274,12 @@
       </c>
       <c r="I243" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #242</t>
+          <t>Invalid Password Rejection - Test Case Iteration #242</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -13324,12 +13324,12 @@
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #243</t>
+          <t>Non-existent User Lookup - Test Case Iteration #243</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="I245" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #244</t>
+          <t>Blank Field Input Validation - Test Case Iteration #244</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #245</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #245</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="I247" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #246</t>
+          <t>New Patient Registration - Test Case Iteration #246</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #247</t>
+          <t>Duplicate Username Check - Test Case Iteration #247</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="I249" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #248</t>
+          <t>Password Confirmation Match - Test Case Iteration #248</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13651,7 +13651,7 @@
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #249</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #249</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #250</t>
+          <t>Latest Assessment Banner - Test Case Iteration #250</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #251</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #251</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
@@ -13774,12 +13774,12 @@
       </c>
       <c r="I253" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #252</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #252</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #253</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #253</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
@@ -13874,12 +13874,12 @@
       </c>
       <c r="I255" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #254</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #254</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #255</t>
+          <t>Diet Plan Generation - Test Case Iteration #255</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I257" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #256</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #256</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -14024,12 +14024,12 @@
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #257</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #257</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I259" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #258</t>
+          <t>Report Download Endpoint - Test Case Iteration #258</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #259</t>
+          <t>Phone Verification OTP - Test Case Iteration #259</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="I261" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #260</t>
+          <t>Page Latency Check - Test Case Iteration #260</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #261</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #261</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
@@ -14274,12 +14274,12 @@
       </c>
       <c r="I263" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #262</t>
+          <t>Invalid Password Rejection - Test Case Iteration #262</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14351,7 +14351,7 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #263</t>
+          <t>Non-existent User Lookup - Test Case Iteration #263</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="I265" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #264</t>
+          <t>Blank Field Input Validation - Test Case Iteration #264</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #265</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #265</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="I267" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #266</t>
+          <t>New Patient Registration - Test Case Iteration #266</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -14524,12 +14524,12 @@
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #267</t>
+          <t>Duplicate Username Check - Test Case Iteration #267</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
@@ -14574,12 +14574,12 @@
       </c>
       <c r="I269" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #268</t>
+          <t>Password Confirmation Match - Test Case Iteration #268</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -14624,12 +14624,12 @@
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #269</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #269</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="I271" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #270</t>
+          <t>Latest Assessment Banner - Test Case Iteration #270</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #271</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #271</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="I273" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #272</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #272</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #273</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #273</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="I275" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #274</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #274</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #275</t>
+          <t>Diet Plan Generation - Test Case Iteration #275</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="I277" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #276</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #276</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #277</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #277</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="I279" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #278</t>
+          <t>Report Download Endpoint - Test Case Iteration #278</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #279</t>
+          <t>Phone Verification OTP - Test Case Iteration #279</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="I281" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #280</t>
+          <t>Page Latency Check - Test Case Iteration #280</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
@@ -15224,12 +15224,12 @@
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Valid Admin Login Verification - Test Case #281</t>
+          <t>Valid Admin Login Verification - Test Case Iteration #281</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="I283" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Invalid Password Rejection - Test Case #282</t>
+          <t>Invalid Password Rejection - Test Case Iteration #282</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
@@ -15324,12 +15324,12 @@
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Non-existent User Lookup - Test Case #283</t>
+          <t>Non-existent User Lookup - Test Case Iteration #283</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="I285" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Blank Field Input Validation - Test Case #284</t>
+          <t>Blank Field Input Validation - Test Case Iteration #284</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
@@ -15424,12 +15424,12 @@
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>SQL Injection Sanitization - Test Case #285</t>
+          <t>SQL Injection Sanitization - Test Case Iteration #285</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
@@ -15474,12 +15474,12 @@
       </c>
       <c r="I287" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>New Patient Registration - Test Case #286</t>
+          <t>New Patient Registration - Test Case Iteration #286</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Duplicate Username Check - Test Case #287</t>
+          <t>Duplicate Username Check - Test Case Iteration #287</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
@@ -15574,12 +15574,12 @@
       </c>
       <c r="I289" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Password Confirmation Match - Test Case #288</t>
+          <t>Password Confirmation Match - Test Case Iteration #288</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Stat Cards Count Verification - Test Case #289</t>
+          <t>Stat Cards Count Verification - Test Case Iteration #289</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="I291" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Latest Assessment Banner - Test Case #290</t>
+          <t>Latest Assessment Banner - Test Case Iteration #290</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Valid Parameter Assessment - Test Case #291</t>
+          <t>Valid Parameter Assessment - Test Case Iteration #291</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="I293" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Glucose Out-of-Bounds Check - Test Case #292</t>
+          <t>Glucose Out-of-Bounds Check - Test Case Iteration #292</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>BMI Auto-Calculator - Test Case #293</t>
+          <t>BMI Auto-Calculator - Test Case Iteration #293</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
@@ -15874,12 +15874,12 @@
       </c>
       <c r="I295" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Risk Gauge Canvas Render - Test Case #294</t>
+          <t>Risk Gauge Canvas Render - Test Case Iteration #294</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
@@ -15924,12 +15924,12 @@
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Diet Plan Generation - Test Case #295</t>
+          <t>Diet Plan Generation - Test Case Iteration #295</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="I297" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Hindi Language Switch (हि) - Test Case #296</t>
+          <t>Hindi Language Switch (हि) - Test Case Iteration #296</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
@@ -16024,12 +16024,12 @@
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Telugu Language Switch (తె) - Test Case #297</t>
+          <t>Telugu Language Switch (తె) - Test Case Iteration #297</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="I299" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Report Download Endpoint - Test Case #298</t>
+          <t>Report Download Endpoint - Test Case Iteration #298</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
@@ -16124,12 +16124,12 @@
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Phone Verification OTP - Test Case #299</t>
+          <t>Phone Verification OTP - Test Case Iteration #299</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="I301" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Page Latency Check - Test Case #300</t>
+          <t>Page Latency Check - Test Case Iteration #300</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:27:14</t>
+          <t>2026-08-09 22:34:44</t>
         </is>
       </c>
     </row>

--- a/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-09 22:34:44</t>
+          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>

--- a/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_Test_Report.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 13:52:57</t>
+          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
